--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/MONTANA_2018.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/MONTANA_2018.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -457,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -488,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -519,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -532,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -545,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -602,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -630,7 +685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -646,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -659,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -690,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -703,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -718,12 +793,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C25">
@@ -734,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C26">
@@ -747,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -760,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Villa Guerrero</t>
@@ -773,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -804,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -817,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -830,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -843,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Santa Cruz de Juventino Rosas</t>
+          <t>Santa Cruz De Juventino Rosas</t>
         </is>
       </c>
       <c r="C34">
@@ -856,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C35">
@@ -869,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -882,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -902,7 +1032,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Atoyac de Álvarez</t>
+          <t>Atoyac De Álvarez</t>
         </is>
       </c>
       <c r="C38">
@@ -913,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -926,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -939,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C41">
@@ -952,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Total</t>
@@ -983,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Huejuquilla el Alto</t>
+          <t>Huejuquilla El Alto</t>
         </is>
       </c>
       <c r="C44">
@@ -996,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -1009,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C46">
@@ -1022,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -1035,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1066,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -1079,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Chilchota</t>
@@ -1092,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Coeneo</t>
@@ -1105,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -1118,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -1131,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -1144,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1175,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1195,7 +1410,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C59">
@@ -1206,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1237,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1268,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C64">
@@ -1281,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1312,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Villa de la Paz</t>
+          <t>Villa De La Paz</t>
         </is>
       </c>
       <c r="C67">
@@ -1325,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1356,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -1369,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1400,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Yécora</t>
@@ -1413,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1444,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -1457,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1488,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -1501,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Huayacocotla</t>
@@ -1514,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -1527,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Poza Rica de Hidalgo</t>
+          <t>Poza Rica De Hidalgo</t>
         </is>
       </c>
       <c r="C82">
@@ -1540,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1563,41 +1863,6 @@
       </c>
       <c r="D84">
         <v>1</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 794,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Diciembre de 2019</t>
-        </is>
       </c>
     </row>
   </sheetData>
